--- a/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,21; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,65</t>
+          <t>-0,91; 2,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,66</t>
+          <t>-1,94; 0,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,27</t>
+          <t>-2,66; -0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,57</t>
+          <t>-1,56; 0,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,3</t>
+          <t>-2,76; -0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,01</t>
+          <t>-0,95; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,07</t>
+          <t>-1,01; 0,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; -0,09</t>
+          <t>-0,79; -0,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 155,75</t>
+          <t>-100,0; 121,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,01</t>
+          <t>-0,9; 2,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,66</t>
+          <t>-1,64; 0,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,9; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,28</t>
+          <t>-2,42; -0,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,58</t>
+          <t>-1,34; 0,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,0</t>
+          <t>-1,53; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,76; -0,3</t>
+          <t>-3,06; -0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,0</t>
+          <t>-0,99; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,05</t>
+          <t>-1,02; 0,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; -0,08</t>
+          <t>-0,72; -0,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,29</t>
+          <t>-100,0; 144,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>-2,18; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,75</t>
+          <t>-0,89; 2,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,66</t>
+          <t>-1,66; 0,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,0</t>
+          <t>-1,74; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,28</t>
+          <t>-2,4; -0,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,57</t>
+          <t>-1,55; 0,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,3</t>
+          <t>-2,77; -0,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,0</t>
+          <t>-0,86; 0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,09</t>
+          <t>-1,07; 0,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; -0,08</t>
+          <t>-0,8; -0,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,81</t>
+          <t>-100,0; 155,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1014-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,133 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.439756763669733</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2078421625287707</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.4629765929343218</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-2,18; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 2,65</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-2.178054863714923</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.894905683315444</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.649510029262267</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-49,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 0,66</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,74; 0,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; -0,27</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.3233818001762719</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.5607805749975113</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.8892156636613867</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.4958124870560077</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-27,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.655374939640717</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.742056065926201</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.397578596242533</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 0,57</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6557842503174584</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>-0.2748301612063545</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +737,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,02</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.429046591496648</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1079006609484098</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2739332220431715</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,92; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,77; -0,3</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.149152650293387</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.549518433611216</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5715406485344667</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3370136669552471</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.016767809192176</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.923004359883034</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.76724795875016</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-0.2990309724604792</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-79,96%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-69,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,86; 0,01</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,07; 0,07</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,8; -0,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 155,75</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.3761236355159014</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4377253100494038</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2678460522958004</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.7996473611079571</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.6980375669060388</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.8594247319647639</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.06867931808731</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.8009759605493222</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.005638168458128463</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.07105830621791004</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-0.08825835616047786</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="n">
+        <v>1.557490036623894</v>
+      </c>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +938,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
